--- a/Assets/Excel/DialogueInfo.xlsx
+++ b/Assets/Excel/DialogueInfo.xlsx
@@ -4,12 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="DialogueInfo" sheetId="1" r:id="rId1"/>
     <sheet name="BranchInfo" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="36">
   <si>
     <t>f_id</t>
   </si>
@@ -101,16 +100,22 @@
     <t>voice,villager</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>年轻人，你可算来了！最近村西的黑森林里老是有野狼出没，村民们都不敢上山砍柴了。</t>
+  </si>
+  <si>
+    <t>我听说你身手不错，能不能帮我们清理一下野狼？</t>
+  </si>
+  <si>
     <t>true</t>
   </si>
   <si>
-    <t>你好，我是这里的村民，有什么可以帮到你的吗？</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>...</t>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>如果你愿意帮忙，我可以把祖传的【猎兽刀】送给你作为谢礼。</t>
   </si>
   <si>
     <t>f_optText</t>
@@ -128,7 +133,10 @@
     <t>该选项选择后的对话信息ID，若为-1，则结束对话</t>
   </si>
   <si>
-    <t>嗯嗯，我知道了</t>
+    <t>没问题！村长放心，我这就去清理野狼</t>
+  </si>
+  <si>
+    <t>抱歉村长，我现在还有别的事，下次再说吧</t>
   </si>
 </sst>
 </file>
@@ -1068,14 +1076,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="7"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="16.4444444444444" customWidth="1"/>
     <col min="2" max="5" width="33.2222222222222" customWidth="1"/>
     <col min="6" max="6" width="24.7777777777778" customWidth="1"/>
     <col min="7" max="7" width="33.2222222222222" customWidth="1"/>
-    <col min="8" max="8" width="60.2222222222222" customWidth="1"/>
+    <col min="8" max="8" width="88.4444444444444" customWidth="1"/>
     <col min="9" max="9" width="30.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1188,9 +1196,7 @@
       <c r="F5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
+      <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
         <v>24</v>
       </c>
@@ -1209,13 +1215,39 @@
         <v>22</v>
       </c>
       <c r="E6" s="1">
+        <v>3</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:8">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="1">
         <v>-1</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="F7" s="3" t="s">
         <v>26</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1228,11 +1260,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="11.8888888888889" customWidth="1"/>
-    <col min="2" max="2" width="25.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="43.4444444444444" customWidth="1"/>
     <col min="3" max="3" width="27.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1241,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1267,13 +1299,13 @@
     </row>
     <row r="4" ht="28.8" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1281,10 +1313,21 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:3">
+      <c r="A6" s="1">
         <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="1">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -1292,16 +1335,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/Assets/Excel/DialogueInfo.xlsx
+++ b/Assets/Excel/DialogueInfo.xlsx
@@ -28,18 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
   <si>
     <t>f_id</t>
   </si>
   <si>
-    <t>f_speakerName</t>
-  </si>
-  <si>
-    <t>f_speakerIcon</t>
-  </si>
-  <si>
-    <t>f_voiceClip</t>
+    <t>f_speakerId</t>
   </si>
   <si>
     <t>f_nextId</t>
@@ -57,25 +51,19 @@
     <t>int</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
-    <t>bool</t>
-  </si>
-  <si>
     <t>key</t>
   </si>
   <si>
     <t>单句对话唯一ID</t>
   </si>
   <si>
-    <t>对话者名称，可以关联NPC配置表，找到对应的NPC信息</t>
-  </si>
-  <si>
-    <t>对话者的头像图标路径，可关联NPC配置表</t>
-  </si>
-  <si>
-    <t>对话者的对应语音，可关联NPC配置表</t>
+    <t>NPC配置表ID</t>
   </si>
   <si>
     <t>该对话的下一条对话信息，若为-1，则对话结束</t>
@@ -91,15 +79,6 @@
     <t>单句对话文本</t>
   </si>
   <si>
-    <t>村民</t>
-  </si>
-  <si>
-    <t>icon,villager</t>
-  </si>
-  <si>
-    <t>voice,villager</t>
-  </si>
-  <si>
     <t>false</t>
   </si>
   <si>
@@ -118,6 +97,9 @@
     <t>如果你愿意帮忙，我可以把祖传的【猎兽刀】送给你作为谢礼。</t>
   </si>
   <si>
+    <t>滚滚滚滚.....</t>
+  </si>
+  <si>
     <t>f_optText</t>
   </si>
   <si>
@@ -137,6 +119,9 @@
   </si>
   <si>
     <t>抱歉村长，我现在还有别的事，下次再说吧</t>
+  </si>
+  <si>
+    <t>...</t>
   </si>
 </sst>
 </file>
@@ -1076,18 +1061,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="7"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16.4444444444444" customWidth="1"/>
-    <col min="2" max="5" width="33.2222222222222" customWidth="1"/>
-    <col min="6" max="6" width="24.7777777777778" customWidth="1"/>
-    <col min="7" max="7" width="33.2222222222222" customWidth="1"/>
-    <col min="8" max="8" width="88.4444444444444" customWidth="1"/>
-    <col min="9" max="9" width="30.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="31.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="33.2222222222222" customWidth="1"/>
+    <col min="4" max="4" width="24.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="33.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="88.4444444444444" customWidth="1"/>
+    <col min="7" max="7" width="30.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1106,148 +1092,130 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" ht="43.2" spans="1:8">
+    </row>
+    <row r="4" ht="43.2" spans="1:6">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
         <v>2</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:8">
+      <c r="D5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:6">
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
         <v>3</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:8">
+      <c r="D6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:6">
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="1" t="s">
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:6">
+      <c r="A8" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="1">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="E7" s="1">
-        <v>-1</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1260,8 +1228,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="11.8888888888889" customWidth="1"/>
     <col min="2" max="2" width="43.4444444444444" customWidth="1"/>
@@ -1273,39 +1241,39 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
     <row r="4" ht="28.8" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1313,7 +1281,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1">
         <v>-1</v>
@@ -1324,9 +1292,20 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:3">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="1">
         <v>-1</v>
       </c>
     </row>
